--- a/METAS.xlsx
+++ b/METAS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samuel\Desktop\DASHBOARDs\dash dauto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3E6BBD3-F9A3-49FD-938C-A790614A1B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6987FA-2C3A-448A-AB9D-814ADC7B2F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{8833B9D8-E3BD-4C53-8526-59DCC59C8BA1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8833B9D8-E3BD-4C53-8526-59DCC59C8BA1}"/>
   </bookViews>
   <sheets>
     <sheet name="DIAS ÚTEIS" sheetId="1" r:id="rId1"/>
@@ -615,7 +615,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">

--- a/METAS.xlsx
+++ b/METAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samuel\Desktop\DASHBOARDs\dash dauto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6987FA-2C3A-448A-AB9D-814ADC7B2F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9BE894-7D06-4933-9B24-995DB57F2AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8833B9D8-E3BD-4C53-8526-59DCC59C8BA1}"/>
   </bookViews>
@@ -615,7 +615,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">

--- a/METAS.xlsx
+++ b/METAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samuel\Desktop\DASHBOARDs\dash dauto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9BE894-7D06-4933-9B24-995DB57F2AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7779E29-3469-49F1-A1EB-0B627E1FC915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8833B9D8-E3BD-4C53-8526-59DCC59C8BA1}"/>
   </bookViews>
@@ -615,7 +615,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>23</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">

--- a/METAS.xlsx
+++ b/METAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samuel\Desktop\DASHBOARDs\dash dauto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7779E29-3469-49F1-A1EB-0B627E1FC915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228D7E5A-F973-47A4-A518-685CA7F82231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8833B9D8-E3BD-4C53-8526-59DCC59C8BA1}"/>
   </bookViews>
@@ -615,7 +615,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>23.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
